--- a/output/pdf_financials_xlsx/NNX.xlsx
+++ b/output/pdf_financials_xlsx/NNX.xlsx
@@ -924,7 +924,7 @@
         <v>0</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>0.000486</v>
       </c>
       <c r="L12" s="3" t="n">
         <v>0</v>
@@ -1661,7 +1661,7 @@
         <v>-0.935237</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-0.6218360000000001</v>
+        <v>-0.622322</v>
       </c>
       <c r="L27" s="3" t="n">
         <v>-0.519854</v>
@@ -1751,7 +1751,7 @@
         <v>-0.935237</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-0.6218360000000001</v>
+        <v>-0.622322</v>
       </c>
       <c r="L29" s="3" t="n">
         <v>-0.519854</v>
@@ -7904,7 +7904,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -18012,7 +18012,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">

--- a/output/pdf_financials_xlsx/NNX.xlsx
+++ b/output/pdf_financials_xlsx/NNX.xlsx
@@ -1126,19 +1126,19 @@
         <v>-0.117608</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>0.213625</v>
+        <v>-0.213625</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>0.094305</v>
+        <v>-0.094305</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>0.142404</v>
+        <v>-0.142404</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>0.103015</v>
+        <v>-0.103015</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>0.09823900000000001</v>
+        <v>-0.09823900000000001</v>
       </c>
       <c r="I17" s="1" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
         <v>-0</v>
       </c>
       <c r="L17" s="3" t="n">
-        <v>0.011152</v>
+        <v>-0.011152</v>
       </c>
       <c r="M17" s="3" t="n">
         <v>-0</v>
@@ -3402,34 +3402,34 @@
         <v>0</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.015626</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>0.12235</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>0.010842</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0</v>
+        <v>0.080427</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0</v>
+        <v>0.16112</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>0</v>
+        <v>0.04625</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0</v>
+        <v>0.03625</v>
       </c>
       <c r="K67" s="3" t="n">
-        <v>0</v>
+        <v>0.0625</v>
       </c>
       <c r="L67" s="3" t="n">
-        <v>0</v>
+        <v>0.07625</v>
       </c>
       <c r="M67" s="3" t="n">
-        <v>0</v>
+        <v>0.08649999999999999</v>
       </c>
     </row>
     <row r="68">
@@ -3445,34 +3445,34 @@
         <v>0</v>
       </c>
       <c r="D68" s="3" t="n">
-        <v>0</v>
+        <v>0.015626</v>
       </c>
       <c r="E68" s="3" t="n">
-        <v>0</v>
+        <v>0.12235</v>
       </c>
       <c r="F68" s="3" t="n">
-        <v>0</v>
+        <v>0.010842</v>
       </c>
       <c r="G68" s="3" t="n">
-        <v>0</v>
+        <v>0.080427</v>
       </c>
       <c r="H68" s="3" t="n">
-        <v>0</v>
+        <v>0.16112</v>
       </c>
       <c r="I68" s="3" t="n">
-        <v>0</v>
+        <v>0.04625</v>
       </c>
       <c r="J68" s="3" t="n">
-        <v>0</v>
+        <v>0.03625</v>
       </c>
       <c r="K68" s="3" t="n">
-        <v>0</v>
+        <v>0.0625</v>
       </c>
       <c r="L68" s="3" t="n">
-        <v>0</v>
+        <v>0.07625</v>
       </c>
       <c r="M68" s="3" t="n">
-        <v>0</v>
+        <v>0.08649999999999999</v>
       </c>
     </row>
     <row r="69">
@@ -3746,34 +3746,34 @@
         <v>1.054577</v>
       </c>
       <c r="D75" s="3" t="n">
-        <v>0.037555</v>
+        <v>0.021929</v>
       </c>
       <c r="E75" s="3" t="n">
-        <v>0.124914</v>
+        <v>0.002564</v>
       </c>
       <c r="F75" s="3" t="n">
-        <v>0.025803</v>
+        <v>0.014961</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>0.100843</v>
+        <v>0.020416</v>
       </c>
       <c r="H75" s="3" t="n">
-        <v>0.265884</v>
+        <v>0.104764</v>
       </c>
       <c r="I75" s="3" t="n">
-        <v>0.393325</v>
+        <v>0.347075</v>
       </c>
       <c r="J75" s="3" t="n">
-        <v>1.811295</v>
+        <v>1.775045</v>
       </c>
       <c r="K75" s="3" t="n">
-        <v>2.121824</v>
+        <v>2.059324</v>
       </c>
       <c r="L75" s="3" t="n">
-        <v>2.533097</v>
+        <v>2.456847</v>
       </c>
       <c r="M75" s="3" t="n">
-        <v>0.999907</v>
+        <v>0.913407</v>
       </c>
     </row>
     <row r="76">
@@ -5260,10 +5260,10 @@
         </is>
       </c>
       <c r="B111" s="3" t="n">
-        <v>0</v>
+        <v>-0.002575</v>
       </c>
       <c r="C111" s="3" t="n">
-        <v>0</v>
+        <v>-0.007172</v>
       </c>
       <c r="D111" s="3" t="n">
         <v>0</v>
@@ -5272,7 +5272,7 @@
         <v>0</v>
       </c>
       <c r="F111" s="3" t="n">
-        <v>0</v>
+        <v>-0.002579</v>
       </c>
       <c r="G111" s="3" t="n">
         <v>0</v>
@@ -6273,10 +6273,10 @@
         </is>
       </c>
       <c r="B134" s="3" t="n">
-        <v>0</v>
+        <v>-0.002575</v>
       </c>
       <c r="C134" s="3" t="n">
-        <v>0</v>
+        <v>-0.007172</v>
       </c>
       <c r="D134" s="3" t="n">
         <v>0</v>
@@ -6285,7 +6285,7 @@
         <v>0</v>
       </c>
       <c r="F134" s="3" t="n">
-        <v>0</v>
+        <v>-0.002579</v>
       </c>
       <c r="G134" s="3" t="n">
         <v>0</v>
@@ -6316,10 +6316,10 @@
         </is>
       </c>
       <c r="B135" s="3" t="n">
-        <v>-1.784664</v>
+        <v>-1.787239</v>
       </c>
       <c r="C135" s="3" t="n">
-        <v>0.262275</v>
+        <v>0.255103</v>
       </c>
       <c r="D135" s="3" t="n">
         <v>-0.262361</v>
@@ -6328,7 +6328,7 @@
         <v>-0.121191</v>
       </c>
       <c r="F135" s="3" t="n">
-        <v>-0.336038</v>
+        <v>-0.338617</v>
       </c>
       <c r="G135" s="3" t="n">
         <v>-0.224433</v>
@@ -12238,7 +12238,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr"/>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E81" t="inlineStr">
         <is>
           <t>-</t>
@@ -13234,7 +13238,11 @@
           <t>Deferred income tax recovery 9</t>
         </is>
       </c>
-      <c r="D96" t="inlineStr"/>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E96" t="inlineStr">
         <is>
           <t>-</t>
@@ -14570,7 +14578,11 @@
           <t>Purchase equipment</t>
         </is>
       </c>
-      <c r="D114" t="inlineStr"/>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E114" t="inlineStr">
         <is>
           <t>-</t>
@@ -14790,7 +14802,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D117" t="inlineStr"/>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E117" t="inlineStr">
         <is>
           <t>-</t>
@@ -15164,7 +15180,11 @@
           <t>Deferred income tax expense (recovery)</t>
         </is>
       </c>
-      <c r="D122" t="inlineStr"/>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E122" t="inlineStr">
         <is>
           <t>-</t>
@@ -15314,7 +15334,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D124" t="inlineStr"/>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E124" t="inlineStr">
         <is>
           <t>-</t>
@@ -15544,7 +15568,11 @@
           <t>Deferred income tax expense</t>
         </is>
       </c>
-      <c r="D127" t="inlineStr"/>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E127" s="5" t="n">
         <v>0.630315</v>
       </c>
@@ -15776,7 +15804,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D130" t="inlineStr"/>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E130" s="5" t="n">
         <v>-0.002575</v>
       </c>
@@ -15928,7 +15960,11 @@
           <t>Proceeds from shares issued for cash</t>
         </is>
       </c>
-      <c r="D132" t="inlineStr"/>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E132" s="5" t="n">
         <v>7</v>
       </c>
@@ -16970,7 +17006,11 @@
           <t>Deferred income tax recovery 9</t>
         </is>
       </c>
-      <c r="D146" t="inlineStr"/>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E146" t="inlineStr">
         <is>
           <t>-</t>
@@ -18392,7 +18432,11 @@
           <t>Deferred income tax recovery 9</t>
         </is>
       </c>
-      <c r="D165" t="inlineStr"/>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E165" t="inlineStr">
         <is>
           <t>-</t>
@@ -20894,7 +20938,11 @@
           <t>Deferred income tax recovery 13</t>
         </is>
       </c>
-      <c r="D199" t="inlineStr"/>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E199" t="inlineStr">
         <is>
           <t>-</t>
@@ -21390,7 +21438,11 @@
           <t>Deferred income tax recovery 14</t>
         </is>
       </c>
-      <c r="D206" t="inlineStr"/>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E206" t="inlineStr">
         <is>
           <t>-</t>
